--- a/results/job_matches_2026-04-19.xlsx
+++ b/results/job_matches_2026-04-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G79"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1098,25 +1098,25 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer</t>
+          <t>Sr Data Scientist</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, MapReduce, HBase, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,102 +1126,102 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68e8bf364a87bcd8</t>
+          <t>https://www.indeed.com/viewjob?jk=c69e0cd00bf5d75b</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr Data Scientist</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c69e0cd00bf5d75b</t>
+          <t>https://www.indeed.com/viewjob?jk=fad382752e6c45e8</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior PS Sales Solutions Architect</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cc1792488693d8a</t>
+          <t>https://www.indeed.com/viewjob?jk=9613eb2ade378a18</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Engineer/ Sr Engineer, IT AI</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Pierre, SD, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, MLOps, MLflow, Jenkins, Maven, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd18edcb36ac9a04</t>
+          <t>https://www.indeed.com/viewjob?jk=c45f8f708d459eac</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Montgomery, AL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a00846a02b4b2ea</t>
+          <t>https://www.indeed.com/viewjob?jk=2ae74230ecf77083</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer II/III</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Okland Construction</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Cheyenne, WY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,17 +1291,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Dataflow, Spark, PySpark, Snowflake, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95e16a542c86ff4d</t>
+          <t>https://www.indeed.com/viewjob?jk=045625da123bda7e</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fad382752e6c45e8</t>
+          <t>https://www.indeed.com/viewjob?jk=93ac2cb123da9211</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9613eb2ade378a18</t>
+          <t>https://www.indeed.com/viewjob?jk=491a518418efe5a9</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pierre, SD, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45f8f708d459eac</t>
+          <t>https://www.indeed.com/viewjob?jk=fb028d0699e5bc93</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Montgomery, AL, US USA</t>
+          <t>Salem, OR, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ae74230ecf77083</t>
+          <t>https://www.indeed.com/viewjob?jk=ffd55914d5888185</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cheyenne, WY, US USA</t>
+          <t>Jefferson City, MO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=045625da123bda7e</t>
+          <t>https://www.indeed.com/viewjob?jk=7dcc0e7131432336</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93ac2cb123da9211</t>
+          <t>https://www.indeed.com/viewjob?jk=73d3be4b73d920a9</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=491a518418efe5a9</t>
+          <t>https://www.indeed.com/viewjob?jk=deec05139dabc08a</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb028d0699e5bc93</t>
+          <t>https://www.indeed.com/viewjob?jk=5550bb7ebf355ee1</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Salem, OR, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffd55914d5888185</t>
+          <t>https://www.indeed.com/viewjob?jk=b3d8d6745d3062a8</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jefferson City, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dcc0e7131432336</t>
+          <t>https://www.indeed.com/viewjob?jk=61d40288b2e57fcb</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73d3be4b73d920a9</t>
+          <t>https://www.indeed.com/viewjob?jk=ed4280fc6cb28b71</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deec05139dabc08a</t>
+          <t>https://www.indeed.com/viewjob?jk=880d7fb467e52950</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Santa Fe, NM, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5550bb7ebf355ee1</t>
+          <t>https://www.indeed.com/viewjob?jk=dc5fd1213b3b70c6</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3d8d6745d3062a8</t>
+          <t>https://www.indeed.com/viewjob?jk=3f84b5e1fdb16e36</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61d40288b2e57fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=a74f10105ffe043c</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4280fc6cb28b71</t>
+          <t>https://www.indeed.com/viewjob?jk=fd07d601c92ea5ee</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=880d7fb467e52950</t>
+          <t>https://www.indeed.com/viewjob?jk=64ce5f46b8cd62e0</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Santa Fe, NM, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc5fd1213b3b70c6</t>
+          <t>https://www.indeed.com/viewjob?jk=16e23fae3491401a</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Augusta, ME, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f84b5e1fdb16e36</t>
+          <t>https://www.indeed.com/viewjob?jk=5d86d173e08711fc</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a74f10105ffe043c</t>
+          <t>https://www.indeed.com/viewjob?jk=b9e35e676e19ee50</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd07d601c92ea5ee</t>
+          <t>https://www.indeed.com/viewjob?jk=0b08ce97d36c85db</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64ce5f46b8cd62e0</t>
+          <t>https://www.indeed.com/viewjob?jk=7a684bacb673ad34</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16e23fae3491401a</t>
+          <t>https://www.indeed.com/viewjob?jk=db4798812a7c7af3</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Augusta, ME, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d86d173e08711fc</t>
+          <t>https://www.indeed.com/viewjob?jk=7698457fecc49833</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Bismarck, ND, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9e35e676e19ee50</t>
+          <t>https://www.indeed.com/viewjob?jk=7ce005b127c47f1d</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Charleston, WV, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b08ce97d36c85db</t>
+          <t>https://www.indeed.com/viewjob?jk=122c1ea0ed721077</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Frankfort, KY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a684bacb673ad34</t>
+          <t>https://www.indeed.com/viewjob?jk=98c6521a48928704</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db4798812a7c7af3</t>
+          <t>https://www.indeed.com/viewjob?jk=0409883540b04233</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7698457fecc49833</t>
+          <t>https://www.indeed.com/viewjob?jk=83979e77477c5e5f</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bismarck, ND, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ce005b127c47f1d</t>
+          <t>https://www.indeed.com/viewjob?jk=08ec46aa032e8c1c</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=122c1ea0ed721077</t>
+          <t>https://www.indeed.com/viewjob?jk=2a86bbd8963f5612</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Frankfort, KY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98c6521a48928704</t>
+          <t>https://www.indeed.com/viewjob?jk=ef9ba3fa89a3f602</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0409883540b04233</t>
+          <t>https://www.indeed.com/viewjob?jk=d3a46e3d7b83b55b</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83979e77477c5e5f</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad20d3e2ae67d22</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Dover, DE, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08ec46aa032e8c1c</t>
+          <t>https://www.indeed.com/viewjob?jk=9576bfc3d6045509</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a86bbd8963f5612</t>
+          <t>https://www.indeed.com/viewjob?jk=a1f2c9d2e9f9ed9f</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef9ba3fa89a3f602</t>
+          <t>https://www.indeed.com/viewjob?jk=a5e05164837c0217</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3a46e3d7b83b55b</t>
+          <t>https://www.indeed.com/viewjob?jk=5a46d719bf637e15</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Montpelier, VT, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad20d3e2ae67d22</t>
+          <t>https://www.indeed.com/viewjob?jk=c9d233e71f6c04c8</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dover, DE, US USA</t>
+          <t>Helena, MT, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9576bfc3d6045509</t>
+          <t>https://www.indeed.com/viewjob?jk=2fc0b0f239ddef48</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1f2c9d2e9f9ed9f</t>
+          <t>https://www.indeed.com/viewjob?jk=520fc4e5451ee86e</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5e05164837c0217</t>
+          <t>https://www.indeed.com/viewjob?jk=1df2a526495b0fdc</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a46d719bf637e15</t>
+          <t>https://www.indeed.com/viewjob?jk=298689cf6faee8a0</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Montpelier, VT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,67 +2841,67 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9d233e71f6c04c8</t>
+          <t>https://www.indeed.com/viewjob?jk=89ef5f7a924752df</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Bioinformatics Cloud Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Helena, MT, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fc0b0f239ddef48</t>
+          <t>https://www.indeed.com/viewjob?jk=70f3b60b1d9a1fb2</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Senior Software Engineer - Production Control Plane</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=520fc4e5451ee86e</t>
+          <t>https://www.indeed.com/viewjob?jk=a5919ca76700b393</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1df2a526495b0fdc</t>
+          <t>https://www.indeed.com/viewjob?jk=581a90bdd18bb399</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=298689cf6faee8a0</t>
+          <t>https://www.indeed.com/viewjob?jk=8f8b1f5f9166b713</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89ef5f7a924752df</t>
+          <t>https://www.indeed.com/viewjob?jk=0515a0bc8f6f1e11</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Veryon</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, BigQuery, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,67 +3051,67 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43792765a0db7bc2</t>
+          <t>https://www.indeed.com/viewjob?jk=319834b7078dd7bb</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Bioinformatics Cloud Engineer</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70f3b60b1d9a1fb2</t>
+          <t>https://www.indeed.com/viewjob?jk=c7e0324e85c38bd3</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Production Control Plane</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,75 +3121,985 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5919ca76700b393</t>
+          <t>https://www.indeed.com/viewjob?jk=57c9b599b447afe5</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Front End UI Developer (Angular)</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, GCP, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2894d188b4dc4e4</t>
+          <t>https://www.indeed.com/viewjob?jk=3f28e52ff13e41e1</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=58139b01da447c8f</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=31eec55a78c92958</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b0f988614f7900ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9a807c5f465bc533</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f6e4c14a86247c39</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0a4a86499506fa74</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6100f68b5c571107</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0268fc51d43f46f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fa3c42c0c29c6fa2</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7d5d2a222e1191b</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=82adfa3031e04de5</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d2c75248cd428f27</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=17b8084c714b559f</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fcafea5b6bbcba68</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2431b916dd05bb6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=417ad0055f64f195</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c473356bf1ce359a</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=790b89847a38e08e</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6c51f57e34f8284d</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a673fb5b1b7d2bd9</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=42748f4cfe75c84a</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ed4c16311ad8ab4d</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f0128cd132590c80</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5720f5caa8ca8d63</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=30932a7fdbb20d57</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc72ec26bd8c9ccd</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
           <t>Machine Learning Engineer II Recommendation Systems- Credit Karma</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B105" t="inlineStr">
         <is>
           <t>Intuit</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C105" t="inlineStr">
         <is>
           <t>Oakland, CA, US USA</t>
         </is>
       </c>
-      <c r="D79" t="n">
+      <c r="D105" t="n">
         <v>10.4</v>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="E105" t="inlineStr">
         <is>
           <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, ETL, Airflow, Python, SQL</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c95ddf0fac17d5df</t>
         </is>

--- a/results/job_matches_2026-04-19.xlsx
+++ b/results/job_matches_2026-04-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,35 +468,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr Cloud Data Architect</t>
+          <t>Software Engineer III - Databricks / IAM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Personify Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>20.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, ECS, RDS, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2e55d4c15c9b5aa</t>
+          <t>https://www.indeed.com/viewjob?jk=2aaafa9ff6580061</t>
         </is>
       </c>
     </row>
@@ -608,25 +608,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Production Control Plane</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5919ca76700b393</t>
+          <t>https://www.indeed.com/viewjob?jk=581a90bdd18bb399</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=581a90bdd18bb399</t>
+          <t>https://www.indeed.com/viewjob?jk=8f8b1f5f9166b713</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f8b1f5f9166b713</t>
+          <t>https://www.indeed.com/viewjob?jk=0515a0bc8f6f1e11</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0515a0bc8f6f1e11</t>
+          <t>https://www.indeed.com/viewjob?jk=319834b7078dd7bb</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=319834b7078dd7bb</t>
+          <t>https://www.indeed.com/viewjob?jk=c7e0324e85c38bd3</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7e0324e85c38bd3</t>
+          <t>https://www.indeed.com/viewjob?jk=57c9b599b447afe5</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57c9b599b447afe5</t>
+          <t>https://www.indeed.com/viewjob?jk=3f28e52ff13e41e1</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f28e52ff13e41e1</t>
+          <t>https://www.indeed.com/viewjob?jk=58139b01da447c8f</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58139b01da447c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=31eec55a78c92958</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31eec55a78c92958</t>
+          <t>https://www.indeed.com/viewjob?jk=b0f988614f7900ce</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0f988614f7900ce</t>
+          <t>https://www.indeed.com/viewjob?jk=9a807c5f465bc533</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a807c5f465bc533</t>
+          <t>https://www.indeed.com/viewjob?jk=f6e4c14a86247c39</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6e4c14a86247c39</t>
+          <t>https://www.indeed.com/viewjob?jk=0a4a86499506fa74</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a4a86499506fa74</t>
+          <t>https://www.indeed.com/viewjob?jk=6100f68b5c571107</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6100f68b5c571107</t>
+          <t>https://www.indeed.com/viewjob?jk=0268fc51d43f46f1</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0268fc51d43f46f1</t>
+          <t>https://www.indeed.com/viewjob?jk=fa3c42c0c29c6fa2</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa3c42c0c29c6fa2</t>
+          <t>https://www.indeed.com/viewjob?jk=e7d5d2a222e1191b</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7d5d2a222e1191b</t>
+          <t>https://www.indeed.com/viewjob?jk=82adfa3031e04de5</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82adfa3031e04de5</t>
+          <t>https://www.indeed.com/viewjob?jk=d2c75248cd428f27</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2c75248cd428f27</t>
+          <t>https://www.indeed.com/viewjob?jk=17b8084c714b559f</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17b8084c714b559f</t>
+          <t>https://www.indeed.com/viewjob?jk=fcafea5b6bbcba68</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcafea5b6bbcba68</t>
+          <t>https://www.indeed.com/viewjob?jk=2431b916dd05bb6d</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2431b916dd05bb6d</t>
+          <t>https://www.indeed.com/viewjob?jk=417ad0055f64f195</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=417ad0055f64f195</t>
+          <t>https://www.indeed.com/viewjob?jk=c473356bf1ce359a</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c473356bf1ce359a</t>
+          <t>https://www.indeed.com/viewjob?jk=790b89847a38e08e</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=790b89847a38e08e</t>
+          <t>https://www.indeed.com/viewjob?jk=6c51f57e34f8284d</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c51f57e34f8284d</t>
+          <t>https://www.indeed.com/viewjob?jk=a673fb5b1b7d2bd9</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a673fb5b1b7d2bd9</t>
+          <t>https://www.indeed.com/viewjob?jk=42748f4cfe75c84a</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42748f4cfe75c84a</t>
+          <t>https://www.indeed.com/viewjob?jk=ed4c16311ad8ab4d</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4c16311ad8ab4d</t>
+          <t>https://www.indeed.com/viewjob?jk=f0128cd132590c80</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0128cd132590c80</t>
+          <t>https://www.indeed.com/viewjob?jk=5720f5caa8ca8d63</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5720f5caa8ca8d63</t>
+          <t>https://www.indeed.com/viewjob?jk=30932a7fdbb20d57</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30932a7fdbb20d57</t>
+          <t>https://www.indeed.com/viewjob?jk=cc72ec26bd8c9ccd</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Machine Learning Engineer II Recommendation Systems- Credit Karma</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, ETL, Airflow, Python, SQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,77 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc72ec26bd8c9ccd</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer II Recommendation Systems- Credit Karma</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Intuit</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Oakland, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, ETL, Airflow, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=c95ddf0fac17d5df</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>St. David's HealthCare</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4e04623dda5e67ab</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-19.xlsx
+++ b/results/job_matches_2026-04-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,70 +538,70 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr Data Scientist</t>
+          <t>Bioinformatics Cloud Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.3</v>
+        <v>12.5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c69e0cd00bf5d75b</t>
+          <t>https://www.indeed.com/viewjob?jk=70f3b60b1d9a1fb2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bioinformatics Cloud Engineer</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70f3b60b1d9a1fb2</t>
+          <t>https://www.indeed.com/viewjob?jk=581a90bdd18bb399</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=581a90bdd18bb399</t>
+          <t>https://www.indeed.com/viewjob?jk=8f8b1f5f9166b713</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f8b1f5f9166b713</t>
+          <t>https://www.indeed.com/viewjob?jk=0515a0bc8f6f1e11</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0515a0bc8f6f1e11</t>
+          <t>https://www.indeed.com/viewjob?jk=319834b7078dd7bb</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=319834b7078dd7bb</t>
+          <t>https://www.indeed.com/viewjob?jk=c7e0324e85c38bd3</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7e0324e85c38bd3</t>
+          <t>https://www.indeed.com/viewjob?jk=57c9b599b447afe5</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57c9b599b447afe5</t>
+          <t>https://www.indeed.com/viewjob?jk=3f28e52ff13e41e1</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f28e52ff13e41e1</t>
+          <t>https://www.indeed.com/viewjob?jk=58139b01da447c8f</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58139b01da447c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=31eec55a78c92958</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31eec55a78c92958</t>
+          <t>https://www.indeed.com/viewjob?jk=b0f988614f7900ce</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0f988614f7900ce</t>
+          <t>https://www.indeed.com/viewjob?jk=9a807c5f465bc533</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a807c5f465bc533</t>
+          <t>https://www.indeed.com/viewjob?jk=f6e4c14a86247c39</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6e4c14a86247c39</t>
+          <t>https://www.indeed.com/viewjob?jk=0a4a86499506fa74</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a4a86499506fa74</t>
+          <t>https://www.indeed.com/viewjob?jk=6100f68b5c571107</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6100f68b5c571107</t>
+          <t>https://www.indeed.com/viewjob?jk=0268fc51d43f46f1</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0268fc51d43f46f1</t>
+          <t>https://www.indeed.com/viewjob?jk=fa3c42c0c29c6fa2</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa3c42c0c29c6fa2</t>
+          <t>https://www.indeed.com/viewjob?jk=e7d5d2a222e1191b</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7d5d2a222e1191b</t>
+          <t>https://www.indeed.com/viewjob?jk=82adfa3031e04de5</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82adfa3031e04de5</t>
+          <t>https://www.indeed.com/viewjob?jk=d2c75248cd428f27</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2c75248cd428f27</t>
+          <t>https://www.indeed.com/viewjob?jk=17b8084c714b559f</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17b8084c714b559f</t>
+          <t>https://www.indeed.com/viewjob?jk=fcafea5b6bbcba68</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcafea5b6bbcba68</t>
+          <t>https://www.indeed.com/viewjob?jk=2431b916dd05bb6d</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2431b916dd05bb6d</t>
+          <t>https://www.indeed.com/viewjob?jk=417ad0055f64f195</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=417ad0055f64f195</t>
+          <t>https://www.indeed.com/viewjob?jk=c473356bf1ce359a</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c473356bf1ce359a</t>
+          <t>https://www.indeed.com/viewjob?jk=790b89847a38e08e</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=790b89847a38e08e</t>
+          <t>https://www.indeed.com/viewjob?jk=6c51f57e34f8284d</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c51f57e34f8284d</t>
+          <t>https://www.indeed.com/viewjob?jk=a673fb5b1b7d2bd9</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a673fb5b1b7d2bd9</t>
+          <t>https://www.indeed.com/viewjob?jk=42748f4cfe75c84a</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42748f4cfe75c84a</t>
+          <t>https://www.indeed.com/viewjob?jk=ed4c16311ad8ab4d</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4c16311ad8ab4d</t>
+          <t>https://www.indeed.com/viewjob?jk=f0128cd132590c80</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0128cd132590c80</t>
+          <t>https://www.indeed.com/viewjob?jk=5720f5caa8ca8d63</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5720f5caa8ca8d63</t>
+          <t>https://www.indeed.com/viewjob?jk=30932a7fdbb20d57</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,77 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30932a7fdbb20d57</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Costa Mesa, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=cc72ec26bd8c9ccd</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer II Recommendation Systems- Credit Karma</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Intuit</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Oakland, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, ETL, Airflow, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c95ddf0fac17d5df</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-19.xlsx
+++ b/results/job_matches_2026-04-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer (Business Analyst IV)</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Fairfax County Government</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>11.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, BigQuery, Cloud Storage, Hadoop, Spark, Scala</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,42 +531,42 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbbe1cdbf051393e</t>
+          <t>https://www.indeed.com/viewjob?jk=581a90bdd18bb399</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bioinformatics Cloud Engineer</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70f3b60b1d9a1fb2</t>
+          <t>https://www.indeed.com/viewjob?jk=8f8b1f5f9166b713</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=581a90bdd18bb399</t>
+          <t>https://www.indeed.com/viewjob?jk=0515a0bc8f6f1e11</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f8b1f5f9166b713</t>
+          <t>https://www.indeed.com/viewjob?jk=319834b7078dd7bb</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0515a0bc8f6f1e11</t>
+          <t>https://www.indeed.com/viewjob?jk=c7e0324e85c38bd3</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=319834b7078dd7bb</t>
+          <t>https://www.indeed.com/viewjob?jk=57c9b599b447afe5</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7e0324e85c38bd3</t>
+          <t>https://www.indeed.com/viewjob?jk=3f28e52ff13e41e1</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57c9b599b447afe5</t>
+          <t>https://www.indeed.com/viewjob?jk=58139b01da447c8f</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f28e52ff13e41e1</t>
+          <t>https://www.indeed.com/viewjob?jk=31eec55a78c92958</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58139b01da447c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=b0f988614f7900ce</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31eec55a78c92958</t>
+          <t>https://www.indeed.com/viewjob?jk=9a807c5f465bc533</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0f988614f7900ce</t>
+          <t>https://www.indeed.com/viewjob?jk=f6e4c14a86247c39</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a807c5f465bc533</t>
+          <t>https://www.indeed.com/viewjob?jk=0a4a86499506fa74</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6e4c14a86247c39</t>
+          <t>https://www.indeed.com/viewjob?jk=6100f68b5c571107</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a4a86499506fa74</t>
+          <t>https://www.indeed.com/viewjob?jk=0268fc51d43f46f1</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6100f68b5c571107</t>
+          <t>https://www.indeed.com/viewjob?jk=fa3c42c0c29c6fa2</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0268fc51d43f46f1</t>
+          <t>https://www.indeed.com/viewjob?jk=e7d5d2a222e1191b</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa3c42c0c29c6fa2</t>
+          <t>https://www.indeed.com/viewjob?jk=82adfa3031e04de5</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7d5d2a222e1191b</t>
+          <t>https://www.indeed.com/viewjob?jk=d2c75248cd428f27</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82adfa3031e04de5</t>
+          <t>https://www.indeed.com/viewjob?jk=17b8084c714b559f</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2c75248cd428f27</t>
+          <t>https://www.indeed.com/viewjob?jk=fcafea5b6bbcba68</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17b8084c714b559f</t>
+          <t>https://www.indeed.com/viewjob?jk=2431b916dd05bb6d</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcafea5b6bbcba68</t>
+          <t>https://www.indeed.com/viewjob?jk=417ad0055f64f195</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2431b916dd05bb6d</t>
+          <t>https://www.indeed.com/viewjob?jk=c473356bf1ce359a</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=417ad0055f64f195</t>
+          <t>https://www.indeed.com/viewjob?jk=790b89847a38e08e</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c473356bf1ce359a</t>
+          <t>https://www.indeed.com/viewjob?jk=6c51f57e34f8284d</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=790b89847a38e08e</t>
+          <t>https://www.indeed.com/viewjob?jk=a673fb5b1b7d2bd9</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c51f57e34f8284d</t>
+          <t>https://www.indeed.com/viewjob?jk=42748f4cfe75c84a</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a673fb5b1b7d2bd9</t>
+          <t>https://www.indeed.com/viewjob?jk=ed4c16311ad8ab4d</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42748f4cfe75c84a</t>
+          <t>https://www.indeed.com/viewjob?jk=f0128cd132590c80</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4c16311ad8ab4d</t>
+          <t>https://www.indeed.com/viewjob?jk=5720f5caa8ca8d63</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0128cd132590c80</t>
+          <t>https://www.indeed.com/viewjob?jk=30932a7fdbb20d57</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1650,76 +1650,6 @@
         </is>
       </c>
       <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5720f5caa8ca8d63</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Sacramento, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=30932a7fdbb20d57</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Costa Mesa, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=cc72ec26bd8c9ccd</t>
         </is>

--- a/results/job_matches_2026-04-19.xlsx
+++ b/results/job_matches_2026-04-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,35 +503,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Architect with AWS and Data Bricks</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Palmetto Tech</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11.1</v>
+        <v>15.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, Lambda, S3, RDS, Google Cloud Platform, Cloud Storage, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=581a90bdd18bb399</t>
+          <t>https://www.indeed.com/viewjob?jk=c581906df4e1c3dd</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f8b1f5f9166b713</t>
+          <t>https://www.indeed.com/viewjob?jk=581a90bdd18bb399</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0515a0bc8f6f1e11</t>
+          <t>https://www.indeed.com/viewjob?jk=8f8b1f5f9166b713</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=319834b7078dd7bb</t>
+          <t>https://www.indeed.com/viewjob?jk=0515a0bc8f6f1e11</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7e0324e85c38bd3</t>
+          <t>https://www.indeed.com/viewjob?jk=319834b7078dd7bb</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57c9b599b447afe5</t>
+          <t>https://www.indeed.com/viewjob?jk=c7e0324e85c38bd3</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f28e52ff13e41e1</t>
+          <t>https://www.indeed.com/viewjob?jk=57c9b599b447afe5</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58139b01da447c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=3f28e52ff13e41e1</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31eec55a78c92958</t>
+          <t>https://www.indeed.com/viewjob?jk=58139b01da447c8f</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0f988614f7900ce</t>
+          <t>https://www.indeed.com/viewjob?jk=31eec55a78c92958</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a807c5f465bc533</t>
+          <t>https://www.indeed.com/viewjob?jk=b0f988614f7900ce</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6e4c14a86247c39</t>
+          <t>https://www.indeed.com/viewjob?jk=9a807c5f465bc533</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a4a86499506fa74</t>
+          <t>https://www.indeed.com/viewjob?jk=f6e4c14a86247c39</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6100f68b5c571107</t>
+          <t>https://www.indeed.com/viewjob?jk=0a4a86499506fa74</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0268fc51d43f46f1</t>
+          <t>https://www.indeed.com/viewjob?jk=6100f68b5c571107</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa3c42c0c29c6fa2</t>
+          <t>https://www.indeed.com/viewjob?jk=0268fc51d43f46f1</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7d5d2a222e1191b</t>
+          <t>https://www.indeed.com/viewjob?jk=fa3c42c0c29c6fa2</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82adfa3031e04de5</t>
+          <t>https://www.indeed.com/viewjob?jk=e7d5d2a222e1191b</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2c75248cd428f27</t>
+          <t>https://www.indeed.com/viewjob?jk=82adfa3031e04de5</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17b8084c714b559f</t>
+          <t>https://www.indeed.com/viewjob?jk=d2c75248cd428f27</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcafea5b6bbcba68</t>
+          <t>https://www.indeed.com/viewjob?jk=17b8084c714b559f</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2431b916dd05bb6d</t>
+          <t>https://www.indeed.com/viewjob?jk=fcafea5b6bbcba68</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=417ad0055f64f195</t>
+          <t>https://www.indeed.com/viewjob?jk=2431b916dd05bb6d</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c473356bf1ce359a</t>
+          <t>https://www.indeed.com/viewjob?jk=417ad0055f64f195</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=790b89847a38e08e</t>
+          <t>https://www.indeed.com/viewjob?jk=c473356bf1ce359a</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c51f57e34f8284d</t>
+          <t>https://www.indeed.com/viewjob?jk=790b89847a38e08e</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a673fb5b1b7d2bd9</t>
+          <t>https://www.indeed.com/viewjob?jk=6c51f57e34f8284d</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42748f4cfe75c84a</t>
+          <t>https://www.indeed.com/viewjob?jk=a673fb5b1b7d2bd9</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4c16311ad8ab4d</t>
+          <t>https://www.indeed.com/viewjob?jk=42748f4cfe75c84a</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0128cd132590c80</t>
+          <t>https://www.indeed.com/viewjob?jk=ed4c16311ad8ab4d</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5720f5caa8ca8d63</t>
+          <t>https://www.indeed.com/viewjob?jk=f0128cd132590c80</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30932a7fdbb20d57</t>
+          <t>https://www.indeed.com/viewjob?jk=5720f5caa8ca8d63</t>
         </is>
       </c>
     </row>
@@ -1633,23 +1633,58 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=30932a7fdbb20d57</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
           <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
-      <c r="D35" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
+      <c r="D36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=cc72ec26bd8c9ccd</t>
         </is>

--- a/results/job_matches_2026-04-19.xlsx
+++ b/results/job_matches_2026-04-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,35 +538,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>AI Engineer (React UI) - Remote US</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Cielo</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Wauwatosa, WI, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=581a90bdd18bb399</t>
+          <t>https://www.indeed.com/viewjob?jk=0e67add270aac4c5</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f8b1f5f9166b713</t>
+          <t>https://www.indeed.com/viewjob?jk=581a90bdd18bb399</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0515a0bc8f6f1e11</t>
+          <t>https://www.indeed.com/viewjob?jk=8f8b1f5f9166b713</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=319834b7078dd7bb</t>
+          <t>https://www.indeed.com/viewjob?jk=0515a0bc8f6f1e11</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7e0324e85c38bd3</t>
+          <t>https://www.indeed.com/viewjob?jk=319834b7078dd7bb</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57c9b599b447afe5</t>
+          <t>https://www.indeed.com/viewjob?jk=c7e0324e85c38bd3</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f28e52ff13e41e1</t>
+          <t>https://www.indeed.com/viewjob?jk=57c9b599b447afe5</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58139b01da447c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=3f28e52ff13e41e1</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31eec55a78c92958</t>
+          <t>https://www.indeed.com/viewjob?jk=58139b01da447c8f</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0f988614f7900ce</t>
+          <t>https://www.indeed.com/viewjob?jk=31eec55a78c92958</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a807c5f465bc533</t>
+          <t>https://www.indeed.com/viewjob?jk=b0f988614f7900ce</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6e4c14a86247c39</t>
+          <t>https://www.indeed.com/viewjob?jk=9a807c5f465bc533</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a4a86499506fa74</t>
+          <t>https://www.indeed.com/viewjob?jk=f6e4c14a86247c39</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6100f68b5c571107</t>
+          <t>https://www.indeed.com/viewjob?jk=0a4a86499506fa74</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0268fc51d43f46f1</t>
+          <t>https://www.indeed.com/viewjob?jk=6100f68b5c571107</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa3c42c0c29c6fa2</t>
+          <t>https://www.indeed.com/viewjob?jk=0268fc51d43f46f1</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7d5d2a222e1191b</t>
+          <t>https://www.indeed.com/viewjob?jk=fa3c42c0c29c6fa2</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82adfa3031e04de5</t>
+          <t>https://www.indeed.com/viewjob?jk=e7d5d2a222e1191b</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2c75248cd428f27</t>
+          <t>https://www.indeed.com/viewjob?jk=82adfa3031e04de5</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17b8084c714b559f</t>
+          <t>https://www.indeed.com/viewjob?jk=d2c75248cd428f27</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcafea5b6bbcba68</t>
+          <t>https://www.indeed.com/viewjob?jk=17b8084c714b559f</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2431b916dd05bb6d</t>
+          <t>https://www.indeed.com/viewjob?jk=fcafea5b6bbcba68</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=417ad0055f64f195</t>
+          <t>https://www.indeed.com/viewjob?jk=2431b916dd05bb6d</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c473356bf1ce359a</t>
+          <t>https://www.indeed.com/viewjob?jk=417ad0055f64f195</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=790b89847a38e08e</t>
+          <t>https://www.indeed.com/viewjob?jk=c473356bf1ce359a</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c51f57e34f8284d</t>
+          <t>https://www.indeed.com/viewjob?jk=790b89847a38e08e</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a673fb5b1b7d2bd9</t>
+          <t>https://www.indeed.com/viewjob?jk=6c51f57e34f8284d</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42748f4cfe75c84a</t>
+          <t>https://www.indeed.com/viewjob?jk=a673fb5b1b7d2bd9</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4c16311ad8ab4d</t>
+          <t>https://www.indeed.com/viewjob?jk=42748f4cfe75c84a</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0128cd132590c80</t>
+          <t>https://www.indeed.com/viewjob?jk=ed4c16311ad8ab4d</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5720f5caa8ca8d63</t>
+          <t>https://www.indeed.com/viewjob?jk=f0128cd132590c80</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30932a7fdbb20d57</t>
+          <t>https://www.indeed.com/viewjob?jk=5720f5caa8ca8d63</t>
         </is>
       </c>
     </row>
@@ -1668,23 +1668,58 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=30932a7fdbb20d57</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
           <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
-      <c r="D36" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
+      <c r="D37" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=cc72ec26bd8c9ccd</t>
         </is>

--- a/results/job_matches_2026-04-19.xlsx
+++ b/results/job_matches_2026-04-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Architect with AWS and Data Bricks</t>
+          <t>AI Engineer (React UI) - Remote US</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Palmetto Tech</t>
+          <t>Cielo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Wauwatosa, WI, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.3</v>
+        <v>11.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Google Cloud Platform, Cloud Storage, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,42 +531,42 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c581906df4e1c3dd</t>
+          <t>https://www.indeed.com/viewjob?jk=0e67add270aac4c5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Engineer (React UI) - Remote US</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cielo</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Wauwatosa, WI, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, CI/CD, Airflow</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e67add270aac4c5</t>
+          <t>https://www.indeed.com/viewjob?jk=581a90bdd18bb399</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=581a90bdd18bb399</t>
+          <t>https://www.indeed.com/viewjob?jk=8f8b1f5f9166b713</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f8b1f5f9166b713</t>
+          <t>https://www.indeed.com/viewjob?jk=0515a0bc8f6f1e11</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0515a0bc8f6f1e11</t>
+          <t>https://www.indeed.com/viewjob?jk=319834b7078dd7bb</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=319834b7078dd7bb</t>
+          <t>https://www.indeed.com/viewjob?jk=c7e0324e85c38bd3</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7e0324e85c38bd3</t>
+          <t>https://www.indeed.com/viewjob?jk=57c9b599b447afe5</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57c9b599b447afe5</t>
+          <t>https://www.indeed.com/viewjob?jk=3f28e52ff13e41e1</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f28e52ff13e41e1</t>
+          <t>https://www.indeed.com/viewjob?jk=58139b01da447c8f</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58139b01da447c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=31eec55a78c92958</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31eec55a78c92958</t>
+          <t>https://www.indeed.com/viewjob?jk=b0f988614f7900ce</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0f988614f7900ce</t>
+          <t>https://www.indeed.com/viewjob?jk=9a807c5f465bc533</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a807c5f465bc533</t>
+          <t>https://www.indeed.com/viewjob?jk=f6e4c14a86247c39</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6e4c14a86247c39</t>
+          <t>https://www.indeed.com/viewjob?jk=0a4a86499506fa74</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a4a86499506fa74</t>
+          <t>https://www.indeed.com/viewjob?jk=6100f68b5c571107</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6100f68b5c571107</t>
+          <t>https://www.indeed.com/viewjob?jk=0268fc51d43f46f1</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0268fc51d43f46f1</t>
+          <t>https://www.indeed.com/viewjob?jk=fa3c42c0c29c6fa2</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa3c42c0c29c6fa2</t>
+          <t>https://www.indeed.com/viewjob?jk=e7d5d2a222e1191b</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7d5d2a222e1191b</t>
+          <t>https://www.indeed.com/viewjob?jk=82adfa3031e04de5</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82adfa3031e04de5</t>
+          <t>https://www.indeed.com/viewjob?jk=d2c75248cd428f27</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2c75248cd428f27</t>
+          <t>https://www.indeed.com/viewjob?jk=17b8084c714b559f</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17b8084c714b559f</t>
+          <t>https://www.indeed.com/viewjob?jk=fcafea5b6bbcba68</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcafea5b6bbcba68</t>
+          <t>https://www.indeed.com/viewjob?jk=2431b916dd05bb6d</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2431b916dd05bb6d</t>
+          <t>https://www.indeed.com/viewjob?jk=417ad0055f64f195</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=417ad0055f64f195</t>
+          <t>https://www.indeed.com/viewjob?jk=c473356bf1ce359a</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c473356bf1ce359a</t>
+          <t>https://www.indeed.com/viewjob?jk=790b89847a38e08e</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=790b89847a38e08e</t>
+          <t>https://www.indeed.com/viewjob?jk=6c51f57e34f8284d</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c51f57e34f8284d</t>
+          <t>https://www.indeed.com/viewjob?jk=a673fb5b1b7d2bd9</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a673fb5b1b7d2bd9</t>
+          <t>https://www.indeed.com/viewjob?jk=42748f4cfe75c84a</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42748f4cfe75c84a</t>
+          <t>https://www.indeed.com/viewjob?jk=ed4c16311ad8ab4d</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4c16311ad8ab4d</t>
+          <t>https://www.indeed.com/viewjob?jk=f0128cd132590c80</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0128cd132590c80</t>
+          <t>https://www.indeed.com/viewjob?jk=5720f5caa8ca8d63</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5720f5caa8ca8d63</t>
+          <t>https://www.indeed.com/viewjob?jk=30932a7fdbb20d57</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1685,41 +1685,6 @@
         </is>
       </c>
       <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=30932a7fdbb20d57</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Costa Mesa, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=cc72ec26bd8c9ccd</t>
         </is>
